--- a/output/profil_klaster_rata_rata.xlsx
+++ b/output/profil_klaster_rata_rata.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,34 +475,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.225</v>
+        <v>0.1742</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0089</v>
+        <v>-0.2124</v>
       </c>
       <c r="D2" t="n">
-        <v>0.002</v>
+        <v>0.0513</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.09420000000000001</v>
+        <v>-0.0863</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0434</v>
+        <v>-0.1696</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1438</v>
+        <v>-0.1561</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0999</v>
+        <v>-0.3751</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0585</v>
+        <v>-0.0664</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.1373</v>
+        <v>-0.2589</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0849</v>
+        <v>0.2477</v>
       </c>
     </row>
     <row r="3">
@@ -512,108 +512,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.3729</v>
+        <v>-0.1004</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0021</v>
+        <v>0.1224</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1456</v>
+        <v>-0.0295</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1748</v>
+        <v>0.0497</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.066</v>
+        <v>0.0977</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1315</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1659</v>
+        <v>0.2161</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0765</v>
+        <v>0.0383</v>
       </c>
       <c r="J3" t="n">
-        <v>0.268</v>
+        <v>0.1491</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1748</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Klaster 3</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>-0.1596</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-0.5448</v>
-      </c>
-      <c r="D4" t="n">
-        <v>-0.3201</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-0.1585</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="G4" t="n">
-        <v>4.2865</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.2138</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.7022</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-0.3716</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1.2506</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Klaster 4</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>-1.0281</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.1018</v>
-      </c>
-      <c r="D5" t="n">
-        <v>7.7974</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-0.1895</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-0.1125</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.2269</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.3319</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-0.7493</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-0.6012</v>
+        <v>-0.1427</v>
       </c>
     </row>
   </sheetData>
